--- a/16. Charts/Charts.xlsx
+++ b/16. Charts/Charts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Advance_Excel_BI\16. Charts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A550A0F4-4A43-4A3F-A151-2F7F691C61ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1E4B1A-D839-4B78-99CA-39A56D7D6091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23151,6 +23151,22 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0800-000001000000}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sparklines!B2:M2</xm:f>
+              <xm:sqref>N2</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
         <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0800-000000000000}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
@@ -23164,22 +23180,6 @@
             <x14:sparkline>
               <xm:f>Sparklines!B3:M3</xm:f>
               <xm:sqref>N3</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0800-000001000000}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Sparklines!B2:M2</xm:f>
-              <xm:sqref>N2</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
